--- a/1.xlsx
+++ b/1.xlsx
@@ -129,7 +129,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,13 +140,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -620,148 +613,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1162,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1174,7 +1167,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1186,7 +1179,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1195,10 +1188,10 @@
         <v>8</v>
       </c>
       <c r="C7" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1209,10 +1202,10 @@
         <v>10</v>
       </c>
       <c r="C8" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1221,10 +1214,10 @@
         <v>11</v>
       </c>
       <c r="C9" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1233,10 +1226,10 @@
         <v>12</v>
       </c>
       <c r="C10" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1247,10 +1240,10 @@
         <v>14</v>
       </c>
       <c r="C11" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1259,10 +1252,10 @@
         <v>15</v>
       </c>
       <c r="C12" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1271,10 +1264,10 @@
         <v>16</v>
       </c>
       <c r="C13" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1283,10 +1276,10 @@
         <v>17</v>
       </c>
       <c r="C14" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1295,10 +1288,10 @@
         <v>18</v>
       </c>
       <c r="C15" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1307,10 +1300,10 @@
         <v>19</v>
       </c>
       <c r="C16" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1358,7 +1351,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1367,7 +1360,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1376,7 +1369,7 @@
         <v>25</v>
       </c>
       <c r="C24" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1387,7 +1380,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1396,7 +1389,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1405,7 +1398,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1416,7 +1409,7 @@
         <v>23</v>
       </c>
       <c r="C28" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1425,7 +1418,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1434,7 +1427,7 @@
         <v>25</v>
       </c>
       <c r="C30" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1445,7 +1438,7 @@
         <v>23</v>
       </c>
       <c r="C31" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1454,7 +1447,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1463,7 +1456,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -1152,10 +1152,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D4" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1164,10 +1164,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D5" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1176,10 +1176,10 @@
         <v>7</v>
       </c>
       <c r="C6" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D6" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1188,10 +1188,10 @@
         <v>8</v>
       </c>
       <c r="C7" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D7" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1202,10 +1202,10 @@
         <v>10</v>
       </c>
       <c r="C8" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D8" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1214,10 +1214,10 @@
         <v>11</v>
       </c>
       <c r="C9" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D9" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1226,10 +1226,10 @@
         <v>12</v>
       </c>
       <c r="C10" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1240,10 +1240,10 @@
         <v>14</v>
       </c>
       <c r="C11" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D11" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1252,10 +1252,10 @@
         <v>15</v>
       </c>
       <c r="C12" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D12" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1264,10 +1264,10 @@
         <v>16</v>
       </c>
       <c r="C13" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1276,10 +1276,10 @@
         <v>17</v>
       </c>
       <c r="C14" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D14" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1288,10 +1288,10 @@
         <v>18</v>
       </c>
       <c r="C15" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D15" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1300,10 +1300,10 @@
         <v>19</v>
       </c>
       <c r="C16" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D16" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1322,7 +1322,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1331,7 +1331,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1340,7 +1340,7 @@
         <v>25</v>
       </c>
       <c r="C21" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1351,7 +1351,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1360,7 +1360,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1369,7 +1369,7 @@
         <v>25</v>
       </c>
       <c r="C24" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1380,7 +1380,7 @@
         <v>23</v>
       </c>
       <c r="C25" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1389,7 +1389,7 @@
         <v>24</v>
       </c>
       <c r="C26" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1398,7 +1398,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1409,7 +1409,7 @@
         <v>23</v>
       </c>
       <c r="C28" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1418,7 +1418,7 @@
         <v>24</v>
       </c>
       <c r="C29" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1427,7 +1427,7 @@
         <v>25</v>
       </c>
       <c r="C30" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1438,7 +1438,7 @@
         <v>23</v>
       </c>
       <c r="C31" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1447,7 +1447,7 @@
         <v>24</v>
       </c>
       <c r="C32" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1456,7 +1456,7 @@
         <v>25</v>
       </c>
       <c r="C33" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
